--- a/output/pdf_financials_xlsx/ACO.X.xlsx
+++ b/output/pdf_financials_xlsx/ACO.X.xlsx
@@ -789,31 +789,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -1389,31 +1389,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>902</v>
+        <v>873</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1073</v>
+        <v>1046</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>921</v>
+        <v>876</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1061</v>
+        <v>995</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>900</v>
+        <v>814</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>371</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>921</v>
+        <v>876</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1061</v>
+        <v>995</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>900</v>
+        <v>814</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>371</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>23.0655129789864</v>
+        <v>22.6699629171817</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.5</v>
+        <v>13.95652173913043</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.500818330605565</v>
+        <v>3.907528641571195</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.26476838079048</v>
+        <v>8.691032724181895</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.38563767778037</v>
+        <v>14.05922126369783</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>18.50140618722379</v>
+        <v>17.59742868621937</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22.37924488504535</v>
+        <v>20.98713351613583</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>18.21125050586807</v>
+        <v>16.47106434641845</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>7.213688508652536</v>
+        <v>5.910946918141162</v>
       </c>
     </row>
     <row r="31">
@@ -2076,31 +2076,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>174</v>
+        <v>1340</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>93</v>
+        <v>833</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>213</v>
+        <v>1069</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>281</v>
+        <v>1248</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>228</v>
+        <v>1130</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>246</v>
+        <v>1277</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>274</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="49">
@@ -3024,19 +3024,19 @@
         <v>47</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>161</v>
+        <v>528</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>240</v>
+        <v>365</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>107</v>
+        <v>655</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>113</v>
+        <v>493</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>87</v>
+        <v>519</v>
       </c>
     </row>
     <row r="76">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E307" s="5" t="n">
@@ -24558,7 +24558,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACO.X.xlsx
+++ b/output/pdf_financials_xlsx/ACO.X.xlsx
@@ -823,31 +823,31 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>380</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>406</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>478</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>484</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>423</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>391</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>434</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>462</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14">
@@ -1389,31 +1389,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>917</v>
+        <v>537</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>642</v>
+        <v>236</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>873</v>
+        <v>395</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1046</v>
+        <v>562</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>603</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>876</v>
+        <v>485</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>995</v>
+        <v>561</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>814</v>
+        <v>352</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>304</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="28">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>917</v>
+        <v>537</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>642</v>
+        <v>236</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>191</v>
+        <v>-287</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>409</v>
+        <v>-75</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>603</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>876</v>
+        <v>485</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>995</v>
+        <v>561</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>814</v>
+        <v>352</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>304</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="30">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>22.6699629171817</v>
+        <v>13.27564894932015</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>13.95652173913043</v>
+        <v>5.130434782608695</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.907528641571195</v>
+        <v>-5.87152209492635</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.691032724181895</v>
+        <v>-1.593710157246069</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.05922126369783</v>
+        <v>4.196782466775472</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>17.59742868621937</v>
+        <v>9.742868621936521</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>20.98713351613583</v>
+        <v>11.83294663573086</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>16.47106434641845</v>
+        <v>7.122622420072846</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.910946918141162</v>
+        <v>-3.597122302158273</v>
       </c>
     </row>
     <row r="31">
@@ -4243,31 +4243,31 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
@@ -4719,31 +4719,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-214</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-294</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-297</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-288</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-291</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-305</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-326</v>
       </c>
     </row>
     <row r="127">
@@ -14187,7 +14187,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>15</v>
       </c>
@@ -15067,7 +15071,11 @@
           <t>Dividends paid to non-controlling interests 28</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -17609,7 +17617,11 @@
           <t>Dividends paid to non-controlling interests 31</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E214" s="5" t="n">
         <v>-187</v>
       </c>
@@ -18341,7 +18353,11 @@
           <t>Proceeds on disposal of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -19388,7 +19404,11 @@
           <t>Dividends paid to non-controlling interests 33 (214)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -21752,7 +21772,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
         <v>-380</v>
       </c>

--- a/output/pdf_financials_xlsx/ACO.X.xlsx
+++ b/output/pdf_financials_xlsx/ACO.X.xlsx
@@ -2851,22 +2851,22 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
@@ -2885,22 +2885,22 @@
         <v>175</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
@@ -3024,19 +3024,19 @@
         <v>47</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>519</v>
+        <v>491</v>
       </c>
     </row>
     <row r="76">
@@ -3191,22 +3191,22 @@
         <v>1.474469228701962</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>1.211504199541868</v>
+        <v>1.213413082209214</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1.27487734306202</v>
+        <v>1.27663857088942</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>1.220757430488974</v>
+        <v>1.222674976030681</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1.312308778536126</v>
+        <v>1.314309249235114</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.34052812858783</v>
+        <v>1.34316877152698</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>1.578153072224219</v>
+        <v>1.581506767277518</v>
       </c>
     </row>
     <row r="81">
@@ -6331,7 +6331,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -7816,7 +7820,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -9441,7 +9449,11 @@
           <t>Lease liabilities 3,20</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
